--- a/artfynd/A 53858-2023 artfynd.xlsx
+++ b/artfynd/A 53858-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119611788</v>
+        <v>127389367</v>
       </c>
       <c r="B2" t="n">
-        <v>96872</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221940</v>
+        <v>6055</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mellanlummer</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium zeilleri</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Rouy) Greuter &amp; Burdet</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Örnberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475203</v>
+        <v>475110</v>
       </c>
       <c r="R2" t="n">
-        <v>6830835</v>
+        <v>6830921</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,36 +740,1406 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>119610633</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>475228</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6830825</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>119711138</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>475222</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6830882</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>119610629</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>475228</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6830825</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>119711134</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>475235</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6830856</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127389407</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>475095</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6830984</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127389408</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>475100</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6830933</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127389307</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>475098</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6831012</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127389308</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>475097</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6830996</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127389309</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>475100</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6830933</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127389310</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>475130</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6830904</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>119611788</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97993</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221940</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mellanlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium zeilleri</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Rouy) Greuter &amp; Burdet</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>475203</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6830835</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Bo karlstens</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Bo karlstens</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127389375</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>475097</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6830996</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127389376</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>475100</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6830933</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127389342</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Örnberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>475089</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6830963</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53858-2023 artfynd.xlsx
+++ b/artfynd/A 53858-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389367</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610633</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119711138</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119610629</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119711134</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389407</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1359,6 +1394,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389408</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389307</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1553,6 +1598,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389308</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1650,6 +1700,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389309</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1747,6 +1802,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389310</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1849,6 +1909,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119611788</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1946,6 +2011,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389375</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2043,6 +2113,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389376</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2140,8 +2215,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127389342</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>